--- a/baselines/BASELINE_v9_WC.xlsx
+++ b/baselines/BASELINE_v9_WC.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1238,16 +1238,16 @@
         <v>Reserves</v>
       </c>
       <c r="B50" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C50">
-        <v>NaN</v>
+        <v>7651348</v>
       </c>
       <c r="D50">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="E50">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
     </row>
     <row r="51">
@@ -1255,16 +1255,16 @@
         <v>Reserves</v>
       </c>
       <c r="B51" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C51">
-        <v>NaN</v>
+        <v>3348984</v>
       </c>
       <c r="D51">
-        <v>NaN</v>
+        <v>3644082</v>
       </c>
       <c r="E51">
-        <v>NaN</v>
+        <v>4295273</v>
       </c>
     </row>
     <row r="52">
@@ -1272,16 +1272,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>4927491</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>5475388</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>6167524</v>
       </c>
     </row>
     <row r="53">
@@ -1289,16 +1289,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="54">
@@ -1306,16 +1306,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="55">
@@ -1323,16 +1323,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>11244050</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>12519064</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>14040516</v>
       </c>
     </row>
     <row r="56">
@@ -1340,50 +1340,50 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C56">
-        <v>8353677</v>
+        <v>7944347</v>
       </c>
       <c r="D56">
-        <v>9300939</v>
+        <v>8845193</v>
       </c>
       <c r="E56">
-        <v>10431290</v>
+        <v>9920156</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B57" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C57">
-        <v>11244050</v>
+        <v>1678558</v>
       </c>
       <c r="D57">
-        <v>12519064</v>
+        <v>1771934</v>
       </c>
       <c r="E57">
-        <v>14040516</v>
+        <v>1870504</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B58" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C58">
-        <v>7944347</v>
+        <v>1771934</v>
       </c>
       <c r="D58">
-        <v>8845193</v>
+        <v>1870504</v>
       </c>
       <c r="E58">
-        <v>9920156</v>
+        <v>1974558</v>
       </c>
     </row>
     <row r="59">
@@ -1391,16 +1391,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C59">
-        <v>1678558</v>
+        <v>18597505</v>
       </c>
       <c r="D59">
-        <v>1771934</v>
+        <v>21345933</v>
       </c>
       <c r="E59">
-        <v>1870504</v>
+        <v>26327567</v>
       </c>
     </row>
     <row r="60">
@@ -1408,16 +1408,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C60">
-        <v>1771934</v>
+        <v>21345933</v>
       </c>
       <c r="D60">
-        <v>1870504</v>
+        <v>26327567</v>
       </c>
       <c r="E60">
-        <v>1974558</v>
+        <v>30430906</v>
       </c>
     </row>
     <row r="61">
@@ -1425,16 +1425,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C61">
-        <v>18597505</v>
+        <v>250164</v>
       </c>
       <c r="D61">
-        <v>21345933</v>
+        <v>250164</v>
       </c>
       <c r="E61">
-        <v>26327567</v>
+        <v>250164</v>
       </c>
     </row>
     <row r="62">
@@ -1442,16 +1442,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C62">
-        <v>21345933</v>
+        <v>23368032</v>
       </c>
       <c r="D62">
-        <v>26327567</v>
+        <v>28448235</v>
       </c>
       <c r="E62">
-        <v>30430906</v>
+        <v>32655628</v>
       </c>
     </row>
     <row r="63">
@@ -1459,16 +1459,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C63">
-        <v>250164</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>250164</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>250164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1476,16 +1476,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C64">
-        <v>23368032</v>
+        <v>289257</v>
       </c>
       <c r="D64">
-        <v>28448235</v>
+        <v>289257</v>
       </c>
       <c r="E64">
-        <v>32655628</v>
+        <v>289257</v>
       </c>
     </row>
     <row r="65">
@@ -1493,16 +1493,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>8642935</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>9590196</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>10720547</v>
       </c>
     </row>
     <row r="66">
@@ -1510,16 +1510,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C66">
-        <v>289257</v>
+        <v>12585622</v>
       </c>
       <c r="D66">
-        <v>289257</v>
+        <v>14725097</v>
       </c>
       <c r="E66">
-        <v>289257</v>
+        <v>18858039</v>
       </c>
     </row>
     <row r="67">
@@ -1527,16 +1527,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C67">
-        <v>8642935</v>
+        <v>14725097</v>
       </c>
       <c r="D67">
-        <v>9590196</v>
+        <v>18858039</v>
       </c>
       <c r="E67">
-        <v>10720547</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="68">
@@ -1544,16 +1544,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C68">
-        <v>12585622</v>
+        <v>14725097</v>
       </c>
       <c r="D68">
-        <v>14725097</v>
+        <v>18858039</v>
       </c>
       <c r="E68">
-        <v>18858039</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="69">
@@ -1561,41 +1561,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C69">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>18858039</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>21935081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B70" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C70">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>18858039</v>
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>21935081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -1643,36 +1643,36 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>0.6684491978609624</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B75" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>0.33155080213903765</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="76">
@@ -1680,16 +1680,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C76">
-        <v>0.6684491978609624</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1697,16 +1697,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C77">
-        <v>0.33155080213903765</v>
+        <v>0.47658261895766835</v>
       </c>
       <c r="D77">
-        <v>0.3315508021390374</v>
+        <v>0.5150468947680041</v>
       </c>
       <c r="E77">
-        <v>0.3315508021390374</v>
+        <v>0.5543931247661993</v>
       </c>
     </row>
     <row r="78">
@@ -1714,16 +1714,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>0.32946877405914593</v>
       </c>
     </row>
     <row r="79">
@@ -1731,16 +1731,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C79">
-        <v>0.47658261895766835</v>
+        <v>0.8060513930168142</v>
       </c>
       <c r="D79">
-        <v>0.5150468947680041</v>
+        <v>0.84451566882715</v>
       </c>
       <c r="E79">
-        <v>0.5543931247661993</v>
+        <v>0.8838618988253453</v>
       </c>
     </row>
     <row r="80">
@@ -1748,16 +1748,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C80">
-        <v>0.3294687740591458</v>
+        <v>14725097</v>
       </c>
       <c r="D80">
-        <v>0.3294687740591459</v>
+        <v>18858039</v>
       </c>
       <c r="E80">
-        <v>0.32946877405914593</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="81">
@@ -1765,16 +1765,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C81">
-        <v>0.8060513930168142</v>
+        <v>6780750</v>
       </c>
       <c r="D81">
-        <v>0.84451566882715</v>
+        <v>10012846</v>
       </c>
       <c r="E81">
-        <v>0.8838618988253453</v>
+        <v>12014925</v>
       </c>
     </row>
     <row r="82">
@@ -1782,16 +1782,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C82">
-        <v>14725097</v>
+        <v>0.8535313651626407</v>
       </c>
       <c r="D82">
-        <v>18858039</v>
+        <v>1.1320098927440445</v>
       </c>
       <c r="E82">
-        <v>21935081</v>
+        <v>1.2111628110596828</v>
       </c>
     </row>
     <row r="83">
@@ -1799,62 +1799,28 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C83">
-        <v>6780750</v>
-      </c>
-      <c r="D83">
-        <v>10012846</v>
-      </c>
-      <c r="E83">
-        <v>12014925</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C84">
-        <v>0.8535313651626407</v>
-      </c>
-      <c r="D84">
-        <v>1.1320098927440445</v>
-      </c>
-      <c r="E84">
-        <v>1.2111628110596828</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B85" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C85" t="str">
+      <c r="C83" t="str">
         <v>Strong</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D83" t="str">
         <v>Strong</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E83" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E83"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2728,16 +2694,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>7651348</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
     </row>
     <row r="53">
@@ -2745,16 +2711,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>3348984</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>3644082</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>4295273</v>
       </c>
     </row>
     <row r="54">
@@ -2762,16 +2728,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>4927491</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>5475388</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>6167524</v>
       </c>
     </row>
     <row r="55">
@@ -2779,16 +2745,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="56">
@@ -2796,16 +2762,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="57">
@@ -2813,16 +2779,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>11244050</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>12519064</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>14040516</v>
       </c>
     </row>
     <row r="58">
@@ -2830,50 +2796,50 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C58">
-        <v>8353677</v>
+        <v>7944347</v>
       </c>
       <c r="D58">
-        <v>9300939</v>
+        <v>8845193</v>
       </c>
       <c r="E58">
-        <v>10431290</v>
+        <v>9920156</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C59">
-        <v>11244050</v>
+        <v>1678558</v>
       </c>
       <c r="D59">
-        <v>12519064</v>
+        <v>1771934</v>
       </c>
       <c r="E59">
-        <v>14040516</v>
+        <v>1870504</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C60">
-        <v>7944347</v>
+        <v>1771934</v>
       </c>
       <c r="D60">
-        <v>8845193</v>
+        <v>1870504</v>
       </c>
       <c r="E60">
-        <v>9920156</v>
+        <v>1974558</v>
       </c>
     </row>
     <row r="61">
@@ -2881,16 +2847,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C61">
-        <v>1678558</v>
+        <v>18597505</v>
       </c>
       <c r="D61">
-        <v>1771934</v>
+        <v>21345933</v>
       </c>
       <c r="E61">
-        <v>1870504</v>
+        <v>26327567</v>
       </c>
     </row>
     <row r="62">
@@ -2898,16 +2864,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C62">
-        <v>1771934</v>
+        <v>21345933</v>
       </c>
       <c r="D62">
-        <v>1870504</v>
+        <v>26327567</v>
       </c>
       <c r="E62">
-        <v>1974558</v>
+        <v>30430906</v>
       </c>
     </row>
     <row r="63">
@@ -2915,16 +2881,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C63">
-        <v>18597505</v>
+        <v>250164</v>
       </c>
       <c r="D63">
-        <v>21345933</v>
+        <v>250164</v>
       </c>
       <c r="E63">
-        <v>26327567</v>
+        <v>250164</v>
       </c>
     </row>
     <row r="64">
@@ -2932,16 +2898,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C64">
-        <v>21345933</v>
+        <v>23368032</v>
       </c>
       <c r="D64">
-        <v>26327567</v>
+        <v>28448235</v>
       </c>
       <c r="E64">
-        <v>30430906</v>
+        <v>32655628</v>
       </c>
     </row>
     <row r="65">
@@ -2949,16 +2915,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C65">
-        <v>250164</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>250164</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>250164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2966,16 +2932,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C66">
-        <v>23368032</v>
+        <v>289257</v>
       </c>
       <c r="D66">
-        <v>28448235</v>
+        <v>289257</v>
       </c>
       <c r="E66">
-        <v>32655628</v>
+        <v>289257</v>
       </c>
     </row>
     <row r="67">
@@ -2983,16 +2949,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>8642935</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>9590196</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>10720547</v>
       </c>
     </row>
     <row r="68">
@@ -3000,16 +2966,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C68">
-        <v>289257</v>
+        <v>12585622</v>
       </c>
       <c r="D68">
-        <v>289257</v>
+        <v>14725097</v>
       </c>
       <c r="E68">
-        <v>289257</v>
+        <v>18858039</v>
       </c>
     </row>
     <row r="69">
@@ -3017,16 +2983,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C69">
-        <v>8642935</v>
+        <v>14725097</v>
       </c>
       <c r="D69">
-        <v>9590196</v>
+        <v>18858039</v>
       </c>
       <c r="E69">
-        <v>10720547</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="70">
@@ -3034,16 +3000,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C70">
-        <v>12585622</v>
+        <v>14725097</v>
       </c>
       <c r="D70">
-        <v>14725097</v>
+        <v>18858039</v>
       </c>
       <c r="E70">
-        <v>18858039</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="71">
@@ -3051,41 +3017,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C71">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>18858039</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>21935081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C72">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>18858039</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>21935081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3102,7 +3068,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3119,7 +3085,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B75" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3133,36 +3099,36 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.6684491978609624</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.33155080213903765</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="78">
@@ -3170,16 +3136,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609624</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3187,16 +3153,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C79">
-        <v>0.33155080213903765</v>
+        <v>0.47658261895766835</v>
       </c>
       <c r="D79">
-        <v>0.3315508021390374</v>
+        <v>0.5150468947680041</v>
       </c>
       <c r="E79">
-        <v>0.3315508021390374</v>
+        <v>0.5543931247661993</v>
       </c>
     </row>
     <row r="80">
@@ -3204,16 +3170,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.32946877405914593</v>
       </c>
     </row>
     <row r="81">
@@ -3221,16 +3187,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C81">
-        <v>0.47658261895766835</v>
+        <v>0.8060513930168142</v>
       </c>
       <c r="D81">
-        <v>0.5150468947680041</v>
+        <v>0.84451566882715</v>
       </c>
       <c r="E81">
-        <v>0.5543931247661993</v>
+        <v>0.8838618988253453</v>
       </c>
     </row>
     <row r="82">
@@ -3238,16 +3204,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C82">
-        <v>0.3294687740591458</v>
+        <v>14725097</v>
       </c>
       <c r="D82">
-        <v>0.3294687740591459</v>
+        <v>18858039</v>
       </c>
       <c r="E82">
-        <v>0.32946877405914593</v>
+        <v>21935081</v>
       </c>
     </row>
     <row r="83">
@@ -3255,16 +3221,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C83">
-        <v>0.8060513930168142</v>
+        <v>6780750</v>
       </c>
       <c r="D83">
-        <v>0.84451566882715</v>
+        <v>10012846</v>
       </c>
       <c r="E83">
-        <v>0.8838618988253453</v>
+        <v>12014925</v>
       </c>
     </row>
     <row r="84">
@@ -3272,16 +3238,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C84">
-        <v>14725097</v>
+        <v>0.8535313651626407</v>
       </c>
       <c r="D84">
-        <v>18858039</v>
+        <v>1.1320098927440445</v>
       </c>
       <c r="E84">
-        <v>21935081</v>
+        <v>1.2111628110596828</v>
       </c>
     </row>
     <row r="85">
@@ -3289,55 +3255,21 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C85">
-        <v>6780750</v>
-      </c>
-      <c r="D85">
-        <v>10012846</v>
-      </c>
-      <c r="E85">
-        <v>12014925</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C86">
-        <v>0.8535313651626407</v>
-      </c>
-      <c r="D86">
-        <v>1.1320098927440445</v>
-      </c>
-      <c r="E86">
-        <v>1.2111628110596828</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C85" t="str">
         <v>Strong</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D85" t="str">
         <v>Strong</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E85" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>